--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.9367740505813</v>
+        <v>4.702225783219461</v>
       </c>
       <c r="D2" t="n">
-        <v>27.91677780369138</v>
+        <v>4.536476393099849</v>
       </c>
       <c r="E2" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F2" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.54883717490606</v>
+        <v>4.801686040922235</v>
       </c>
       <c r="D3" t="n">
-        <v>28.92171927150511</v>
+        <v>4.699779381619582</v>
       </c>
       <c r="E3" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F3" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.67061880773276</v>
+        <v>5.471475556256573</v>
       </c>
       <c r="D4" t="n">
-        <v>33.2881139130577</v>
+        <v>5.409318510871876</v>
       </c>
       <c r="E4" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F4" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.02905184456758</v>
+        <v>5.529720924742231</v>
       </c>
       <c r="D5" t="n">
-        <v>33.54715698829042</v>
+        <v>5.451413010597193</v>
       </c>
       <c r="E5" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F5" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.9407259482267</v>
+        <v>5.02786796658684</v>
       </c>
       <c r="D6" t="n">
-        <v>30.69645407334278</v>
+        <v>4.988173786918202</v>
       </c>
       <c r="E6" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F6" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.02627790863272</v>
+        <v>4.066770160152817</v>
       </c>
       <c r="D7" t="n">
-        <v>25.55219968832534</v>
+        <v>4.152232449352868</v>
       </c>
       <c r="E7" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F7" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.05896465463964</v>
+        <v>2.772081756378942</v>
       </c>
       <c r="D8" t="n">
-        <v>18.08586023733734</v>
+        <v>2.938952288567318</v>
       </c>
       <c r="E8" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F8" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.75536426649028</v>
+        <v>3.860246693304671</v>
       </c>
       <c r="D9" t="n">
-        <v>24.74165595021055</v>
+        <v>4.020519091909215</v>
       </c>
       <c r="E9" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F9" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.86302297391391</v>
+        <v>4.365241233261012</v>
       </c>
       <c r="D10" t="n">
-        <v>27.80843124496586</v>
+        <v>4.518870077306952</v>
       </c>
       <c r="E10" t="n">
-        <v>5.030631018849668</v>
+        <v>0.8174775405630711</v>
       </c>
       <c r="F10" t="n">
-        <v>4.49155914902301</v>
+        <v>0.7298783617162391</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
